--- a/SuppTable6.xlsx
+++ b/SuppTable6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anczuo\Box\Intron retention in STAT2 regulates STAT2 function and predicts response to immunotherapy in lung adenocarcinoma\REVISION 2\For upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/englar/Documents/Banchereau_Lab/Paper_Writing/Long Read RNA Sequencing Identifies Intron Retention as a Major Regulator of STAT2 Function in Lung Adenocarcinoma/SCIENCE/Galley_Proofs/Supplementary Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F59342-1A1D-4992-B925-54F9F17BCB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13286C18-4A77-CB48-9EC4-73EAA6EAACE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BDEB000C-688A-124A-BBC1-85A803D7ADEA}"/>
+    <workbookView xWindow="960" yWindow="1660" windowWidth="29040" windowHeight="15840" xr2:uid="{BDEB000C-688A-124A-BBC1-85A803D7ADEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="1" r:id="rId1"/>
@@ -1091,6 +1091,287 @@
     <t>Table S6E. Nucleofection conditions</t>
   </si>
   <si>
+    <t>Table S6G. Donor oligonucleotide sequence</t>
+  </si>
+  <si>
+    <t>Table S6H. Primers for cloning</t>
+  </si>
+  <si>
+    <t>Table S6I. Antibodies used for western blot</t>
+  </si>
+  <si>
+    <t>Table S6J. Antibodies used for immunofluorescence</t>
+  </si>
+  <si>
+    <t>Table S6K. ViewRNA probes</t>
+  </si>
+  <si>
+    <t>ri12-ASO1</t>
+  </si>
+  <si>
+    <t>ri12-ASO2</t>
+  </si>
+  <si>
+    <t>ri6-ASO1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">STAT2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ri12 extended</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">STAT2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ri6 extended</t>
+    </r>
+  </si>
+  <si>
+    <t>STAT2_ri6_1F</t>
+  </si>
+  <si>
+    <t>AAACACCTGTGGAGAGCCAG</t>
+  </si>
+  <si>
+    <t>STAT2_e9_7R</t>
+  </si>
+  <si>
+    <t>STAT2_e8_1F</t>
+  </si>
+  <si>
+    <t>STAT2_ri12_1R</t>
+  </si>
+  <si>
+    <t>TGCAGTTCCTCTGTCACACC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. RT-PCR primers used for semi-quantitative PCR of AS events</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. qPCR primers used for gene expression quantification</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Splice-switching antisense oligonucleotides</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. gRNA sequence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Nucleofection conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Donor oligonucleotide sequence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Primers for cloning</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Antibodies used for western blot</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6J</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Antibodies used for immunofluorescence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Table S6K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. ViewRNA probes</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Table S6F. Primers for confirmation of </t>
     </r>
@@ -1113,79 +1394,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> knockouts</t>
-    </r>
-  </si>
-  <si>
-    <t>Table S6G. Donor oligonucleotide sequence</t>
-  </si>
-  <si>
-    <t>Table S6H. Primers for cloning</t>
-  </si>
-  <si>
-    <t>Table S6I. Antibodies used for western blot</t>
-  </si>
-  <si>
-    <t>Table S6J. Antibodies used for immunofluorescence</t>
-  </si>
-  <si>
-    <t>Table S6K. ViewRNA probes</t>
-  </si>
-  <si>
-    <t>ri12-ASO1</t>
-  </si>
-  <si>
-    <t>ri12-ASO2</t>
-  </si>
-  <si>
-    <t>ri6-ASO1</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">STAT2 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ri12 extended</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">STAT2 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ri6 extended</t>
-    </r>
-  </si>
-  <si>
-    <t>STAT2_ri6_1F</t>
-  </si>
-  <si>
-    <t>AAACACCTGTGGAGAGCCAG</t>
-  </si>
-  <si>
-    <t>STAT2_e9_7R</t>
-  </si>
-  <si>
-    <t>STAT2_e8_1F</t>
-  </si>
-  <si>
-    <t>STAT2_ri12_1R</t>
-  </si>
-  <si>
-    <t>TGCAGTTCCTCTGTCACACC</t>
+      <t xml:space="preserve"> gene editing</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1196,7 +1406,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Table S6A</t>
+      <t>Table S6F</t>
     </r>
     <r>
       <rPr>
@@ -1205,19 +1415,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>. RT-PCR primers used for semi-quantitative PCR of AS events</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t xml:space="preserve">. Primers for confirmation of </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Table S6B</t>
+      <t>STAT2</t>
     </r>
     <r>
       <rPr>
@@ -1226,196 +1434,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>. qPCR primers used for gene expression quantification</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Splice-switching antisense oligonucleotides</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. gRNA sequence</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Nucleofection conditions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Primers for confirmation of STAT2 knockouts</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Donor oligonucleotide sequence</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Primers for cloning</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Antibodies used for western blot</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6J</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Antibodies used for immunofluorescence</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Table S6K</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>. ViewRNA probes</t>
+      <t xml:space="preserve"> gene editing</t>
     </r>
   </si>
 </sst>
@@ -1423,7 +1442,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1546,6 +1565,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -2000,69 +2026,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B67B8B-00B9-1442-B78E-2A962D1F3D1E}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="16384" width="10.88671875" style="27"/>
+    <col min="1" max="16384" width="10.85546875" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75">
+    <row r="1" spans="1:1">
       <c r="A1" s="19" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75">
+    <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="2" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="2" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.75">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:1">
+      <c r="A8" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75">
-      <c r="A8" s="2" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15.75">
-      <c r="A9" s="2" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="2" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15.75">
-      <c r="A10" s="2" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15.75">
-      <c r="A11" s="2" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" s="2" t="s">
         <v>287</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="15.75">
-      <c r="A12" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="15.75">
-      <c r="A13" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -2073,14 +2099,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93058575-258D-FC42-9DBC-808BEDC63793}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
+    <row r="1" spans="1:7">
       <c r="A1" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2301,14 +2327,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6350EA-009D-AB46-AD8B-6CD05ADB9E7B}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
+    <row r="1" spans="1:7">
       <c r="A1" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2437,15 +2463,15 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1709D42F-184E-AC4E-B3C8-FD3D4023BDE0}">
   <dimension ref="A1:B111"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2">
       <c r="A1" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -3330,16 +3356,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AAE1C37-B579-DD49-99D9-333B6A9FC5EE}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10">
       <c r="A1" s="9" t="s">
         <v>257</v>
       </c>
@@ -3365,7 +3391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.95" customHeight="1">
+    <row r="4" spans="1:10" ht="16" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>24</v>
       </c>
@@ -3382,7 +3408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.95" customHeight="1">
+    <row r="5" spans="1:10" ht="16" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>29</v>
       </c>
@@ -3403,16 +3429,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>275</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>21</v>
@@ -3420,19 +3446,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>277</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3443,15 +3469,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4328076-2FE6-8F45-963C-3618A69BD5D6}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5">
       <c r="A1" s="17" t="s">
         <v>258</v>
       </c>
@@ -3541,14 +3567,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC3D206-ECBE-1B48-A747-3E1535C69D18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:3">
       <c r="A1" s="9" t="s">
         <v>259</v>
       </c>
@@ -3568,7 +3594,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>45</v>
@@ -3579,7 +3605,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>46</v>
@@ -3590,7 +3616,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>46</v>
@@ -3618,15 +3644,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24332A2-0186-5644-A653-BCEAB5AB6FAF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:3">
       <c r="A1" s="17" t="s">
         <v>260</v>
       </c>
@@ -3674,12 +3700,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C33F8F7-FEC4-DF43-AAB7-7399CE414752}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:3">
       <c r="A1" s="17" t="s">
         <v>261</v>
       </c>
@@ -3727,16 +3753,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D3430C-3A7F-DB41-804B-DE2BA964D949}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.33203125" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:3">
       <c r="A1" s="17" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3826,15 +3852,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68AA6E48-BE7D-5A42-884C-12395C3CF699}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="201.33203125" customWidth="1"/>
+    <col min="2" max="2" width="201.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2">
       <c r="A1" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B1" s="18"/>
     </row>
@@ -3862,15 +3888,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E4B4E9C-904A-C24C-B660-14170B90E9ED}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="105.88671875" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="105.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2">
       <c r="A1" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B1" s="1"/>
     </row>
